--- a/docs/DocumentoRequisitosPMA.xlsx
+++ b/docs/DocumentoRequisitosPMA.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\Repo\product-management-app\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7699AF52-F103-40A5-B7C0-D65EFA18B602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24E1FFD-72EC-4411-8EA3-20C0E11F6970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RequisitosFuncionais" sheetId="1" r:id="rId1"/>
     <sheet name="RegrasNegocio" sheetId="2" r:id="rId2"/>
+    <sheet name="RequisitosNãoFuncionais" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="100">
   <si>
     <t xml:space="preserve">Nome do Sistema: </t>
   </si>
@@ -29,22 +30,13 @@
     <t>Product Management App</t>
   </si>
   <si>
-    <t>Requisitos Funcionais</t>
-  </si>
-  <si>
     <t>Visão geral</t>
   </si>
   <si>
     <t>Detalhes</t>
   </si>
   <si>
-    <t>Regras de Negócio</t>
-  </si>
-  <si>
     <t>RF01</t>
-  </si>
-  <si>
-    <t>O sistema deve permitir o cadastro de produto</t>
   </si>
   <si>
     <t>O produto é cadastrado com
@@ -60,20 +52,7 @@
 -&gt; Status</t>
   </si>
   <si>
-    <t xml:space="preserve">-&gt; Para cadastrar produto, é preciso estar associado a uma categoria existente
--&gt; Ao cadastrar deve salvar automaticamente a data de criação, ultima atualização e usuário que fez o cadastro
--&gt; Os campos de preenchimento efetivos são Nome, Descrição, Quantidade, Imagem, Preço e Status
--&gt; O status inclui disponível ou não disponível, refletindo com a quantidade 
--&gt; O nome deve ser único
--&gt; O preço deve estar na unidade Reais, 
--&gt; Campos numéricos devem ser não negativos
--&gt; Data de Criação deve estar no formato DD-MM-YYYY HH:MM:SS, de acordo com o intervalo temporal </t>
-  </si>
-  <si>
     <t>RF02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O sistema deve permitir a edição do produto </t>
   </si>
   <si>
     <t>Cada produto tem uma opção de editar:
@@ -86,42 +65,19 @@
 -&gt; Status</t>
   </si>
   <si>
-    <t>-&gt; Ao editar produto, deve salvar a data e hora da atualização e usuário associado</t>
-  </si>
-  <si>
     <t>RF03</t>
   </si>
   <si>
-    <t>O sistema deve permitir a remoção de produto</t>
-  </si>
-  <si>
     <t>Cada produto deve ter uma opção de remover dos registros</t>
   </si>
   <si>
-    <t xml:space="preserve">-&gt; O sistema deve abrir uma janela de confirmação antes de efetuar a remoção
--&gt; Ao efetuar a remoção, deve salvar a data e hora da remoção e o usuário associado
--&gt; O email deve ser único
--&gt; Data de criação deve estar no formato DD-MM-YYYY HH:MM:SS </t>
-  </si>
-  <si>
     <t>RF04</t>
   </si>
   <si>
-    <t>O sistema deve permitir a visualização do produto</t>
-  </si>
-  <si>
     <t>O sistema mantêm uma visão de tabela mostrando todos os registros de produtos</t>
   </si>
   <si>
     <t>RF05</t>
-  </si>
-  <si>
-    <t>O sistema deve permitir o gerenciamento de categorias</t>
-  </si>
-  <si>
-    <t>O sistema permite cadastrar, editar, remover e visualizar os campos:
--&gt; nome
--&gt; descrição</t>
   </si>
   <si>
     <t>RF06</t>
@@ -139,23 +95,10 @@
 -&gt; Ativo no sistema</t>
   </si>
   <si>
-    <t>-&gt; Para cadastrar usuário, é preciso estar associado a uma categoria existente
--&gt; Ao cadastrar deve salvar automaticamente a data de criação do usuário</t>
-  </si>
-  <si>
     <t>RF07</t>
   </si>
   <si>
     <t>O sistema deve permitir o cadastro de funções dos usuários</t>
-  </si>
-  <si>
-    <t>-&gt; Uma função pode ser criada com um nome e identificador, e o nível de 
-acesso no sistema</t>
-  </si>
-  <si>
-    <t>-&gt; A função deve ser única
--&gt; A função admin deve ser ser o valor padrão do sistema
--&gt; O nível de acesso deve refletir nas permissões e funções do usuário</t>
   </si>
   <si>
     <t>RF08</t>
@@ -172,12 +115,6 @@
 -&gt; Ultimas movimentações de produtos</t>
   </si>
   <si>
-    <t>-&gt; Os dados devem refletir nos registros atuais
--&gt; O sistema deve atualizar dinamicamente a página a cada 30 segundos
--&gt; O painel deve ser navegável
--&gt; A mensagem deve incluir o nome do usuário que fez o login</t>
-  </si>
-  <si>
     <t>RF09</t>
   </si>
   <si>
@@ -189,10 +126,6 @@
 -&gt; Senha</t>
   </si>
   <si>
-    <t>-&gt; Se errar a senha, deve informar ao usuário
--&gt; A cada 10 tentativas deve bloquear o acesso temporariamente</t>
-  </si>
-  <si>
     <t>RF10</t>
   </si>
   <si>
@@ -202,10 +135,6 @@
     <t>Os usuários podem fazer logout pela botão no canto superior</t>
   </si>
   <si>
-    <t>-&gt; O usuário deve retornar a página de login, após logout
--&gt; Mostra um feedback de logout</t>
-  </si>
-  <si>
     <t>RF11</t>
   </si>
   <si>
@@ -215,13 +144,6 @@
     <t>O usuário consegue recuperar senha via e-mail na página de login, com link de acesso único com a nova senha</t>
   </si>
   <si>
-    <t>-&gt; A opção de recuperar senha deve aparecer após 3 tentativas de erro
--&gt; O e-mail deve ser uma entrada válida nos registros
--&gt; Um link de acesso único deve ser enviado ao e-mail do usuário
--&gt; A nova senha deve ser atualizada nos registros
--&gt; Após alterar senha com sucesso, deve redirecionar para página de login e feedback</t>
-  </si>
-  <si>
     <t>Regra de Negócio</t>
   </si>
   <si>
@@ -229,13 +151,218 @@
   </si>
   <si>
     <t>RN01</t>
+  </si>
+  <si>
+    <t>Para cadastrar produto, é preciso estar associado a uma categoria existente</t>
+  </si>
+  <si>
+    <t>RN02</t>
+  </si>
+  <si>
+    <t>RN03</t>
+  </si>
+  <si>
+    <t>RN04</t>
+  </si>
+  <si>
+    <t>O nome deve ser único</t>
+  </si>
+  <si>
+    <t>O preço deve estar na unidade de Reais</t>
+  </si>
+  <si>
+    <t>Campos numéricos devem ser não negativos</t>
+  </si>
+  <si>
+    <t>RN06</t>
+  </si>
+  <si>
+    <t>RN07</t>
+  </si>
+  <si>
+    <t>RNF01</t>
+  </si>
+  <si>
+    <t>RNF02</t>
+  </si>
+  <si>
+    <t>RNF03</t>
+  </si>
+  <si>
+    <t>RNF04</t>
+  </si>
+  <si>
+    <t>RNF05</t>
+  </si>
+  <si>
+    <t>Data de Criação deve estar no formato DD-MM-YYYY HH:MM:SS, de acordo com o intervalo temporal de Manaus</t>
+  </si>
+  <si>
+    <t>Fonte</t>
+  </si>
+  <si>
+    <t>Ao editar produto, deve salvar a data e hora da atualização e usuário associado</t>
+  </si>
+  <si>
+    <t>O email deve ser único</t>
+  </si>
+  <si>
+    <t>RN08</t>
+  </si>
+  <si>
+    <t>Ao efetuar a remoção, deve salvar a data e hora da remoção e o usuário associado</t>
+  </si>
+  <si>
+    <t>O sistema deve abrir uma janela de confirmação antes de efetuar a remoção</t>
+  </si>
+  <si>
+    <t>RN09</t>
+  </si>
+  <si>
+    <t>RN10</t>
+  </si>
+  <si>
+    <t>Ao cadastrar deve salvar automaticamente a data de criação do usuário</t>
+  </si>
+  <si>
+    <t>RN11</t>
+  </si>
+  <si>
+    <t>RN12</t>
+  </si>
+  <si>
+    <t>A função cadastrada deve ser única</t>
+  </si>
+  <si>
+    <t>RN13</t>
+  </si>
+  <si>
+    <t>A função admin deve ser ser o valor padrão do sistema</t>
+  </si>
+  <si>
+    <t>RN14</t>
+  </si>
+  <si>
+    <t>RN15</t>
+  </si>
+  <si>
+    <t>O nível de acesso deve refletir nas permissões e funções do usuário</t>
+  </si>
+  <si>
+    <t>RN16</t>
+  </si>
+  <si>
+    <t>RN18</t>
+  </si>
+  <si>
+    <t>O usuário deve retornar a página de login, após logout</t>
+  </si>
+  <si>
+    <t>RN19</t>
+  </si>
+  <si>
+    <t>RN20</t>
+  </si>
+  <si>
+    <t>A opção de recuperar senha deve aparecer após 3 tentativas de erro</t>
+  </si>
+  <si>
+    <t>Requisito Não Funcional</t>
+  </si>
+  <si>
+    <t>RF</t>
+  </si>
+  <si>
+    <t>Implementação</t>
+  </si>
+  <si>
+    <t>Situação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avaliar </t>
+  </si>
+  <si>
+    <t>O sistema deve permitir o cadastro de produto por um usuário autenticado</t>
+  </si>
+  <si>
+    <t>O sistema deve permitir a edição dos dados de um produto existente</t>
+  </si>
+  <si>
+    <t>O sistema deve permitir a remoção de um produto existente</t>
+  </si>
+  <si>
+    <t>O sistema deve permitir a visualização dos produtos cadastrados em tabela</t>
+  </si>
+  <si>
+    <t>O sistema permite cadastrar, editar, remover e acesso dos usuários por meio de funções:
+&gt; admin
+&gt; gerente
+&gt; lojista
+&gt; usuário</t>
+  </si>
+  <si>
+    <t>O sistema deve permitir o gerenciamento de acesso dos usuários por funções</t>
+  </si>
+  <si>
+    <t>Uma função pode ser criada com um nome descrição e nível de acesso</t>
+  </si>
+  <si>
+    <t>Observação</t>
+  </si>
+  <si>
+    <t>Verificar comportamento</t>
+  </si>
+  <si>
+    <t>Confimar limitação</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Consistência</t>
+  </si>
+  <si>
+    <t>Validação</t>
+  </si>
+  <si>
+    <t>Para cadastrar usuário, é preciso estar associado a uma função existente</t>
+  </si>
+  <si>
+    <t>Modelo de Dados</t>
+  </si>
+  <si>
+    <t>O status inclui disponível ou não disponível</t>
+  </si>
+  <si>
+    <t>Esclarecer o que seria valor padrão</t>
+  </si>
+  <si>
+    <t>Quais permissões correspodem a cada nível?</t>
+  </si>
+  <si>
+    <t>O painel administrativo deve refletir nos registros atuais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O sistema deve informar feedbacks das ações do usuário </t>
+  </si>
+  <si>
+    <t>Verificar comportamento relacionado as tentativas de erro</t>
+  </si>
+  <si>
+    <t>Um link de recuperação de senha acesso único deve ser enviado ao e-mail do usuário</t>
+  </si>
+  <si>
+    <t>A nova senha deve ser substituir a senha anterior do usuário, após recuperação de senha</t>
+  </si>
+  <si>
+    <t>Os campos de preenchimento obrigatórios são Nome, Descrição, Preço, Data de Criação e Ultima Atualização</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -245,6 +372,11 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -269,10 +401,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -497,216 +632,614 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="71.28515625" customWidth="1"/>
-    <col min="4" max="4" width="29.140625" customWidth="1"/>
+    <col min="1" max="1" width="20.28515625" customWidth="1"/>
+    <col min="2" max="2" width="44.28515625" customWidth="1"/>
+    <col min="3" max="3" width="42.7109375" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="140.25" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="B4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="D4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="102" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+      <c r="D6" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D7" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="B8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="123.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+      <c r="C10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+      <c r="D11" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="D12" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D14" s="2" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7B4B3DB-70E0-4CDA-8E35-941329F178EB}">
-  <dimension ref="C3:D4"/>
+  <dimension ref="C3:G24"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" customWidth="1"/>
+    <col min="4" max="4" width="77.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" customWidth="1"/>
+    <col min="6" max="6" width="24.42578125" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G3" t="s">
         <v>48</v>
       </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="4" spans="3:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="3:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="3:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="3:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F9" t="s">
+        <v>88</v>
+      </c>
+      <c r="G9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="3:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="3:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="4" spans="3:4" ht="409.5" x14ac:dyDescent="0.2">
-      <c r="C4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="E11" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="3:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="3:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="3:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="3:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="3:7" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="C16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="3:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="3:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G18" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="3:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="C19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="3:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G20" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="3:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G21" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="F23" s="3"/>
+    </row>
+    <row r="24" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="F24" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07D0BCDD-93A6-4DD5-8CAE-17C5DBE19FA5}">
+  <dimension ref="B2:F7"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="13.85546875" customWidth="1"/>
+    <col min="3" max="3" width="38.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="B2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>